--- a/excel/capacity-to-deadline-optimizer_dashboard.xlsx
+++ b/excel/capacity-to-deadline-optimizer_dashboard.xlsx
@@ -288,6 +288,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_by_specialty'!$A$2:$A$7</f>
@@ -316,6 +317,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_by_specialty'!$A$2:$A$7</f>
@@ -340,6 +342,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -353,6 +356,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -465,6 +469,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_by_specialty_2'!$A$2:$A$7</f>
@@ -489,6 +494,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -517,6 +523,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -565,6 +572,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_reminder'!$A$2:$A$3</f>
@@ -589,6 +597,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -617,6 +626,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -665,6 +675,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_lead_bands'!$A$2:$A$5</f>
@@ -693,6 +704,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_lead_bands'!$A$2:$A$5</f>
@@ -717,6 +729,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -730,6 +743,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -782,6 +796,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_fill_sim'!$A$2:$A$4</f>
@@ -847,6 +862,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -875,6 +891,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <valAx>
         <axId val="200"/>
@@ -983,6 +1000,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -1010,6 +1028,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -1058,6 +1077,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_time_block'!$A$2:$A$3</f>
@@ -1086,6 +1106,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_time_block'!$A$2:$A$3</f>
@@ -1110,6 +1131,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -1123,6 +1145,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
